--- a/Reports/01_saiwaki_ren_作業報告.xlsx
+++ b/Reports/01_saiwaki_ren_作業報告.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teacher\Documents\GitHub\assignment2-uic-tickets\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="75">
   <si>
     <t>■進級制作　作業報告書</t>
     <rPh sb="1" eb="3">
@@ -3364,6 +3364,82 @@
     </rPh>
     <rPh sb="198" eb="200">
       <t>ソウシン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>蒲池</t>
+    <rPh sb="0" eb="2">
+      <t>カマチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・斉脇さんの出席番号は 05 なのでこのファイル名を
+05_saiwaki_ren_作業報告 に修正してください。
+やり方がわからない場合は相談してください。
+・氏名の欄（E2)が「蒲池 雅也」のままなので、自分の名前に書き換えてください
+・シート名も「蒲池雅也」のままなので、自分の名前に書き換えてください
+・翌日の予定の記載もお願いします。</t>
+    <rPh sb="1" eb="3">
+      <t>サイワキ</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>シュッセキバンゴウ</t>
+    </rPh>
+    <rPh sb="24" eb="25">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="48" eb="50">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="60" eb="61">
+      <t>カタ</t>
+    </rPh>
+    <rPh sb="67" eb="69">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="70" eb="72">
+      <t>ソウダン</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="84" eb="85">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="91" eb="93">
+      <t>カマチ</t>
+    </rPh>
+    <rPh sb="94" eb="96">
+      <t>マサヤ</t>
+    </rPh>
+    <rPh sb="104" eb="106">
+      <t>ジブン</t>
+    </rPh>
+    <rPh sb="107" eb="109">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="110" eb="111">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="112" eb="113">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="124" eb="125">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="156" eb="158">
+      <t>ヨクジツ</t>
+    </rPh>
+    <rPh sb="159" eb="161">
+      <t>ヨテイ</t>
+    </rPh>
+    <rPh sb="162" eb="164">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="166" eb="167">
+      <t>ネガ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -4410,8 +4486,12 @@
       <c r="C5" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="13"/>
+      <c r="D5" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="108" customHeight="1">
       <c r="A6" s="12"/>
